--- a/excelTemplate/collectTemplate.xlsx
+++ b/excelTemplate/collectTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/liudong/workspace/xiangmeng/git/zhongtan/zhongtan-server/excelTemplate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33754F2F-A988-2940-86B0-E7BE0E9332B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{036CE11C-ABCA-3344-801E-D15BCA4C5C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="28000" windowHeight="11700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">票据统计汇总表!$A$2:$AE$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">票据统计汇总表!$A$2:$AJ$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">[1]COSCO!$C$3:$H$14</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
     <t>收据开具清单统计汇总表</t>
   </si>
@@ -174,63 +174,71 @@
   </si>
   <si>
     <t xml:space="preserve">Receipt No. </t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Bank</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>&lt;%=rs1.invoice_masterbi_check_no%&gt;</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>&lt;%=rs1.invoice_masterbi_bank_reference_no%&gt;</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Vessel Voyage</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>&lt;%=rs1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>invoice_vessel_voyage</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>%&gt;</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>DO FEE</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>&lt;%=rs1.invoice_masterbi_do_fee%&gt;</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>&lt;%=rs1.invoice_masterbi_cod_charge%&gt;</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t> Refund User </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t> Refund Time </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t> Refund Check No./Payment Serial No.  </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Refund</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;%=rs1.invoice_vessel_voyage%&gt;</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;%=rs1.refund_deposit%&gt;</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;%=rs1.refund_deposit_user%&gt;</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;%=rs1.refund_deposit_time%&gt;</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;%=rs1.refund_deposit_remark%&gt;</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -243,7 +251,7 @@
     <numFmt numFmtId="178" formatCode="#,##0_ "/>
     <numFmt numFmtId="179" formatCode="#,##0.00_ "/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -267,15 +275,6 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -329,14 +328,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -400,23 +399,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="40" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="40" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="40" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -750,7 +746,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AH3"/>
+  <dimension ref="A1:AJ3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.1640625" style="1" customWidth="1"/>
@@ -779,18 +775,18 @@
     <col min="31" max="31" width="12.1640625" style="1" customWidth="1"/>
     <col min="32" max="32" width="18.33203125" style="1" customWidth="1"/>
     <col min="33" max="33" width="21.6640625" style="1" customWidth="1"/>
-    <col min="34" max="34" width="9.33203125" style="1" customWidth="1"/>
-    <col min="35" max="35" width="17.83203125" style="1" customWidth="1"/>
-    <col min="36" max="36" width="11.6640625" style="1" customWidth="1"/>
+    <col min="34" max="34" width="19.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="26.33203125" style="1" customWidth="1"/>
+    <col min="36" max="36" width="45.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="37" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="22.25" customHeight="1">
+    <row r="1" spans="1:36" ht="22.25" customHeight="1">
       <c r="J1" s="16" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:34" ht="28.5" customHeight="1">
+    <row r="2" spans="1:36" ht="28.5" customHeight="1">
       <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
@@ -876,7 +872,7 @@
         <v>26</v>
       </c>
       <c r="AC2" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AD2" s="20" t="s">
         <v>27</v>
@@ -887,9 +883,20 @@
       <c r="AF2" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="AH2" s="21"/>
+      <c r="AG2" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="AH2" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="AI2" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="AJ2" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
-    <row r="3" spans="1:34" ht="18" customHeight="1">
+    <row r="3" spans="1:36" ht="18" customHeight="1">
       <c r="A3" s="8" t="s">
         <v>29</v>
       </c>
@@ -902,7 +909,7 @@
       <c r="D3" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="E3" s="24" t="s">
         <v>33</v>
       </c>
       <c r="F3" s="14" t="s">
@@ -924,57 +931,68 @@
       <c r="L3" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="M3" s="24" t="s">
+      <c r="M3" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="N3" s="24" t="s">
+      <c r="N3" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="O3" s="24" t="s">
+      <c r="O3" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
-      <c r="S3" s="24" t="s">
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22"/>
+      <c r="R3" s="22"/>
+      <c r="S3" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="T3" s="24" t="s">
+      <c r="T3" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="U3" s="24"/>
-      <c r="V3" s="24" t="s">
+      <c r="U3" s="22"/>
+      <c r="V3" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="W3" s="24" t="s">
+      <c r="W3" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="X3" s="24"/>
-      <c r="Y3" s="24"/>
-      <c r="Z3" s="24"/>
-      <c r="AA3" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="AB3" s="24" t="s">
+      <c r="X3" s="22"/>
+      <c r="Y3" s="22"/>
+      <c r="Z3" s="22"/>
+      <c r="AA3" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB3" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="AC3" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD3" s="24" t="s">
+      <c r="AC3" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="AD3" s="22" t="s">
         <v>46</v>
       </c>
       <c r="AE3" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="AF3" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="AH3" s="22"/>
+      <c r="AF3" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="AG3" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH3" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI3" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ3" s="25" t="s">
+        <v>64</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AE3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <autoFilter ref="A2:AJ2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.35416666666666702" right="0.35416666666666702" top="0.74791666666666701" bottom="0.74791666666666701" header="0.31388888888888899" footer="0.31388888888888899"/>
   <pageSetup paperSize="9" scale="28" orientation="portrait"/>
 </worksheet>
